--- a/artfynd/A 63441-2025 artfynd.xlsx
+++ b/artfynd/A 63441-2025 artfynd.xlsx
@@ -1443,48 +1443,41 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130930217</v>
+        <v>130930226</v>
       </c>
       <c r="B8" t="n">
-        <v>79500</v>
+        <v>91829</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6459</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Flot.) Kullh.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448392</v>
+        <v>448362</v>
       </c>
       <c r="R8" t="n">
-        <v>7037298</v>
+        <v>7037345</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1525,23 +1518,27 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1559,41 +1556,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130930226</v>
+        <v>130930217</v>
       </c>
       <c r="B9" t="n">
-        <v>91829</v>
+        <v>79500</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6459</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Lopadium disciforme</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>448362</v>
+        <v>448392</v>
       </c>
       <c r="R9" t="n">
-        <v>7037345</v>
+        <v>7037298</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1634,27 +1638,23 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -2140,32 +2140,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130930219</v>
+        <v>130930230</v>
       </c>
       <c r="B14" t="n">
-        <v>92531</v>
+        <v>78256</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>228579</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448355</v>
+        <v>448404</v>
       </c>
       <c r="R14" t="n">
-        <v>7037273</v>
+        <v>7037411</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2257,10 +2257,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130930230</v>
+        <v>130930220</v>
       </c>
       <c r="B15" t="n">
-        <v>78256</v>
+        <v>79715</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2268,21 +2268,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228579</v>
+        <v>1797</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>448404</v>
+        <v>448353</v>
       </c>
       <c r="R15" t="n">
-        <v>7037411</v>
+        <v>7037267</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2374,32 +2374,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130930220</v>
+        <v>130930219</v>
       </c>
       <c r="B16" t="n">
-        <v>79715</v>
+        <v>92531</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1797</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2409,10 +2409,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>448353</v>
+        <v>448355</v>
       </c>
       <c r="R16" t="n">
-        <v>7037267</v>
+        <v>7037273</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130930231</v>
+        <v>130930223</v>
       </c>
       <c r="B19" t="n">
-        <v>83224</v>
+        <v>79715</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2735,21 +2735,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>1797</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2759,10 +2759,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>448412</v>
+        <v>448337</v>
       </c>
       <c r="R19" t="n">
-        <v>7037419</v>
+        <v>7037328</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2841,32 +2841,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130930222</v>
+        <v>130930231</v>
       </c>
       <c r="B20" t="n">
-        <v>83222</v>
+        <v>83224</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6486</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448330</v>
+        <v>448412</v>
       </c>
       <c r="R20" t="n">
-        <v>7037323</v>
+        <v>7037419</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2958,32 +2958,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130930223</v>
+        <v>130930222</v>
       </c>
       <c r="B21" t="n">
-        <v>79715</v>
+        <v>83222</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1797</v>
+        <v>6486</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2993,10 +2993,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448337</v>
+        <v>448330</v>
       </c>
       <c r="R21" t="n">
-        <v>7037328</v>
+        <v>7037323</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 63441-2025 artfynd.xlsx
+++ b/artfynd/A 63441-2025 artfynd.xlsx
@@ -1443,41 +1443,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130930226</v>
+        <v>130930217</v>
       </c>
       <c r="B8" t="n">
-        <v>91829</v>
+        <v>79500</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6459</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Lopadium disciforme</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448362</v>
+        <v>448392</v>
       </c>
       <c r="R8" t="n">
-        <v>7037345</v>
+        <v>7037298</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1518,27 +1525,23 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1556,48 +1559,41 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130930217</v>
+        <v>130930226</v>
       </c>
       <c r="B9" t="n">
-        <v>79500</v>
+        <v>91829</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6459</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Flot.) Kullh.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>448392</v>
+        <v>448362</v>
       </c>
       <c r="R9" t="n">
-        <v>7037298</v>
+        <v>7037345</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1638,23 +1634,27 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130930223</v>
+        <v>130930231</v>
       </c>
       <c r="B19" t="n">
-        <v>79715</v>
+        <v>83224</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2735,21 +2735,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1797</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2759,10 +2759,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>448337</v>
+        <v>448412</v>
       </c>
       <c r="R19" t="n">
-        <v>7037328</v>
+        <v>7037419</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2841,32 +2841,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130930231</v>
+        <v>130930222</v>
       </c>
       <c r="B20" t="n">
-        <v>83224</v>
+        <v>83222</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6486</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448412</v>
+        <v>448330</v>
       </c>
       <c r="R20" t="n">
-        <v>7037419</v>
+        <v>7037323</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2958,32 +2958,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130930222</v>
+        <v>130930223</v>
       </c>
       <c r="B21" t="n">
-        <v>83222</v>
+        <v>79715</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6486</v>
+        <v>1797</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2993,10 +2993,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448330</v>
+        <v>448337</v>
       </c>
       <c r="R21" t="n">
-        <v>7037323</v>
+        <v>7037328</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3396,7 +3396,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131064804</v>
+        <v>131064799</v>
       </c>
       <c r="B25" t="n">
         <v>57884</v>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>448308</v>
+        <v>448242</v>
       </c>
       <c r="R25" t="n">
-        <v>7037158</v>
+        <v>7037242</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3498,7 +3498,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131064799</v>
+        <v>131064804</v>
       </c>
       <c r="B26" t="n">
         <v>57884</v>
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>448242</v>
+        <v>448308</v>
       </c>
       <c r="R26" t="n">
-        <v>7037242</v>
+        <v>7037158</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 63441-2025 artfynd.xlsx
+++ b/artfynd/A 63441-2025 artfynd.xlsx
@@ -2140,10 +2140,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130930230</v>
+        <v>130930220</v>
       </c>
       <c r="B14" t="n">
-        <v>78256</v>
+        <v>79715</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,21 +2151,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228579</v>
+        <v>1797</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448404</v>
+        <v>448353</v>
       </c>
       <c r="R14" t="n">
-        <v>7037411</v>
+        <v>7037267</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2257,32 +2257,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130930220</v>
+        <v>130930219</v>
       </c>
       <c r="B15" t="n">
-        <v>79715</v>
+        <v>92531</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1797</v>
+        <v>3298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>448353</v>
+        <v>448355</v>
       </c>
       <c r="R15" t="n">
-        <v>7037267</v>
+        <v>7037273</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2374,32 +2374,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130930219</v>
+        <v>130930230</v>
       </c>
       <c r="B16" t="n">
-        <v>92531</v>
+        <v>78256</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>228579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2409,10 +2409,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>448355</v>
+        <v>448404</v>
       </c>
       <c r="R16" t="n">
-        <v>7037273</v>
+        <v>7037411</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2841,32 +2841,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130930222</v>
+        <v>130930223</v>
       </c>
       <c r="B20" t="n">
-        <v>83222</v>
+        <v>79715</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6486</v>
+        <v>1797</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448330</v>
+        <v>448337</v>
       </c>
       <c r="R20" t="n">
-        <v>7037323</v>
+        <v>7037328</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2958,32 +2958,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130930223</v>
+        <v>130930222</v>
       </c>
       <c r="B21" t="n">
-        <v>79715</v>
+        <v>83222</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1797</v>
+        <v>6486</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2993,10 +2993,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448337</v>
+        <v>448330</v>
       </c>
       <c r="R21" t="n">
-        <v>7037328</v>
+        <v>7037323</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3396,7 +3396,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131064799</v>
+        <v>131064804</v>
       </c>
       <c r="B25" t="n">
         <v>57884</v>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>448242</v>
+        <v>448308</v>
       </c>
       <c r="R25" t="n">
-        <v>7037242</v>
+        <v>7037158</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3498,7 +3498,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131064804</v>
+        <v>131064799</v>
       </c>
       <c r="B26" t="n">
         <v>57884</v>
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>448308</v>
+        <v>448242</v>
       </c>
       <c r="R26" t="n">
-        <v>7037158</v>
+        <v>7037242</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 63441-2025 artfynd.xlsx
+++ b/artfynd/A 63441-2025 artfynd.xlsx
@@ -1446,7 +1446,7 @@
         <v>130930217</v>
       </c>
       <c r="B8" t="n">
-        <v>79500</v>
+        <v>79501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>130930226</v>
       </c>
       <c r="B9" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>130930221</v>
       </c>
       <c r="B10" t="n">
-        <v>79715</v>
+        <v>79716</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>130930232</v>
       </c>
       <c r="B11" t="n">
-        <v>83222</v>
+        <v>83223</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>130930225</v>
       </c>
       <c r="B12" t="n">
-        <v>79715</v>
+        <v>79716</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>130930227</v>
       </c>
       <c r="B13" t="n">
-        <v>83224</v>
+        <v>83225</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2140,32 +2140,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130930220</v>
+        <v>130930219</v>
       </c>
       <c r="B14" t="n">
-        <v>79715</v>
+        <v>92532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1797</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448353</v>
+        <v>448355</v>
       </c>
       <c r="R14" t="n">
-        <v>7037267</v>
+        <v>7037273</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2257,32 +2257,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130930219</v>
+        <v>130930230</v>
       </c>
       <c r="B15" t="n">
-        <v>92531</v>
+        <v>78257</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3298</v>
+        <v>228579</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>448355</v>
+        <v>448404</v>
       </c>
       <c r="R15" t="n">
-        <v>7037273</v>
+        <v>7037411</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2374,10 +2374,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130930230</v>
+        <v>130930220</v>
       </c>
       <c r="B16" t="n">
-        <v>78256</v>
+        <v>79716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2385,21 +2385,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>1797</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2409,10 +2409,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>448404</v>
+        <v>448353</v>
       </c>
       <c r="R16" t="n">
-        <v>7037411</v>
+        <v>7037267</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2494,7 +2494,7 @@
         <v>130930216</v>
       </c>
       <c r="B17" t="n">
-        <v>80349</v>
+        <v>80350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>130930218</v>
       </c>
       <c r="B18" t="n">
-        <v>79715</v>
+        <v>79716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130930231</v>
+        <v>130930223</v>
       </c>
       <c r="B19" t="n">
-        <v>83224</v>
+        <v>79716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2735,21 +2735,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>1797</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2759,10 +2759,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>448412</v>
+        <v>448337</v>
       </c>
       <c r="R19" t="n">
-        <v>7037419</v>
+        <v>7037328</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130930223</v>
+        <v>130930231</v>
       </c>
       <c r="B20" t="n">
-        <v>79715</v>
+        <v>83225</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2852,21 +2852,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1797</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448337</v>
+        <v>448412</v>
       </c>
       <c r="R20" t="n">
-        <v>7037328</v>
+        <v>7037419</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2961,7 +2961,7 @@
         <v>130930222</v>
       </c>
       <c r="B21" t="n">
-        <v>83222</v>
+        <v>83223</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>130930228</v>
       </c>
       <c r="B22" t="n">
-        <v>83222</v>
+        <v>83223</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 63441-2025 artfynd.xlsx
+++ b/artfynd/A 63441-2025 artfynd.xlsx
@@ -2257,10 +2257,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130930230</v>
+        <v>130930220</v>
       </c>
       <c r="B15" t="n">
-        <v>78257</v>
+        <v>79716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2268,21 +2268,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228579</v>
+        <v>1797</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>448404</v>
+        <v>448353</v>
       </c>
       <c r="R15" t="n">
-        <v>7037411</v>
+        <v>7037267</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2374,10 +2374,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130930220</v>
+        <v>130930230</v>
       </c>
       <c r="B16" t="n">
-        <v>79716</v>
+        <v>78257</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2385,21 +2385,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1797</v>
+        <v>228579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2409,10 +2409,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>448353</v>
+        <v>448404</v>
       </c>
       <c r="R16" t="n">
-        <v>7037267</v>
+        <v>7037411</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 63441-2025 artfynd.xlsx
+++ b/artfynd/A 63441-2025 artfynd.xlsx
@@ -2257,10 +2257,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130930220</v>
+        <v>130930230</v>
       </c>
       <c r="B15" t="n">
-        <v>79716</v>
+        <v>78257</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2268,21 +2268,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1797</v>
+        <v>228579</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>448353</v>
+        <v>448404</v>
       </c>
       <c r="R15" t="n">
-        <v>7037267</v>
+        <v>7037411</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2374,10 +2374,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130930230</v>
+        <v>130930220</v>
       </c>
       <c r="B16" t="n">
-        <v>78257</v>
+        <v>79716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2385,21 +2385,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>1797</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2409,10 +2409,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>448404</v>
+        <v>448353</v>
       </c>
       <c r="R16" t="n">
-        <v>7037411</v>
+        <v>7037267</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 63441-2025 artfynd.xlsx
+++ b/artfynd/A 63441-2025 artfynd.xlsx
@@ -3195,7 +3195,7 @@
         <v>131064798</v>
       </c>
       <c r="B23" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>131064797</v>
       </c>
       <c r="B24" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>131064804</v>
       </c>
       <c r="B25" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>131064799</v>
       </c>
       <c r="B26" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>131064796</v>
       </c>
       <c r="B27" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>131064802</v>
       </c>
       <c r="B28" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>131064800</v>
       </c>
       <c r="B29" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 63441-2025 artfynd.xlsx
+++ b/artfynd/A 63441-2025 artfynd.xlsx
@@ -3195,7 +3195,7 @@
         <v>131064798</v>
       </c>
       <c r="B23" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>131064797</v>
       </c>
       <c r="B24" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>131064804</v>
       </c>
       <c r="B25" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>131064799</v>
       </c>
       <c r="B26" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>131064796</v>
       </c>
       <c r="B27" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>131064802</v>
       </c>
       <c r="B28" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>131064800</v>
       </c>
       <c r="B29" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 63441-2025 artfynd.xlsx
+++ b/artfynd/A 63441-2025 artfynd.xlsx
@@ -3195,7 +3195,7 @@
         <v>131064798</v>
       </c>
       <c r="B23" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>131064797</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>131064804</v>
       </c>
       <c r="B25" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>131064799</v>
       </c>
       <c r="B26" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>131064796</v>
       </c>
       <c r="B27" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>131064802</v>
       </c>
       <c r="B28" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>131064800</v>
       </c>
       <c r="B29" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 63441-2025 artfynd.xlsx
+++ b/artfynd/A 63441-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1923046</v>
+        <v>441052</v>
       </c>
       <c r="B2" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>1797</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448225.351300379</v>
+        <v>448225</v>
       </c>
       <c r="R2" t="n">
-        <v>7037295.095980085</v>
+        <v>7037295</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -749,19 +744,9 @@
           <t>2002-06-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2002-06-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,54 +788,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>776085</v>
+        <v>130930218</v>
       </c>
       <c r="B3" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>1797</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hällbergets NObrant, V om Hällsjön, V om Offerdals kyrka, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448307.0495397726</v>
+        <v>448364</v>
       </c>
       <c r="R3" t="n">
-        <v>7037223.095942911</v>
+        <v>7037293</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +853,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2002-06-24</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2002-06-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,49 +870,49 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>granskog, på bark av levande rönn i 120 årig granskog,</t>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Rönn</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr"/>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>malin almquist</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Lst Z Artdatabas</t>
-        </is>
-      </c>
+          <t>Jesper Wadstein, Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>441052</v>
+        <v>130930220</v>
       </c>
       <c r="B4" t="n">
-        <v>77959</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -965,20 +934,19 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hällbergets NObrant, V om Hällsjön, V om Offerdals kyrka, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448225.351300379</v>
+        <v>448353</v>
       </c>
       <c r="R4" t="n">
-        <v>7037295.095980085</v>
+        <v>7037267</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,22 +970,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2002-06-24</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2002-06-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,84 +987,83 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>granskog, på bark av levande gran i 120 årig granskog,</t>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Gran</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr"/>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>malin almquist</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Lst Z Artdatabas</t>
-        </is>
-      </c>
+          <t>Jesper Wadstein, Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1963114</v>
+        <v>130930221</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1797</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hällbergets NObrant, V om Hällsjön, V om Offerdals kyrka, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448307.0495397726</v>
+        <v>448331</v>
       </c>
       <c r="R5" t="n">
-        <v>7037223.095942911</v>
+        <v>7037320</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1130,22 +1087,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2002-06-24</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2002-06-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,84 +1104,83 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>granskog, på bark av levande rönn i 120 årig granskog,</t>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Rönn</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr"/>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>malin almquist</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Lst Z Artdatabas</t>
-        </is>
-      </c>
+          <t>Jesper Wadstein, Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>776086</v>
+        <v>130930223</v>
       </c>
       <c r="B6" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>1797</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hällbergets NObrant, V om Hällsjön, V om Offerdals kyrka, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>448225.351300379</v>
+        <v>448337</v>
       </c>
       <c r="R6" t="n">
-        <v>7037295.095980085</v>
+        <v>7037328</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1258,22 +1204,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2002-06-24</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2002-06-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,84 +1221,83 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>granskog, på bark av levande sälg i 120 årig granskog,</t>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Salix</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr"/>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>malin almquist</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Lst Z Artdatabas</t>
-        </is>
-      </c>
+          <t>Jesper Wadstein, Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1963115</v>
+        <v>130930225</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1797</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hällbergets NObrant, V om Hällsjön, V om Offerdals kyrka, Jmt</t>
+          <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448225.351300379</v>
+        <v>448356</v>
       </c>
       <c r="R7" t="n">
-        <v>7037295.095980085</v>
+        <v>7037357</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1386,22 +1321,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2002-06-24</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2002-06-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1413,81 +1338,84 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>granskog, på bark av levande sälg i 120 årig granskog,</t>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Salix</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr"/>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>malin almquist</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulrika Nordin</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Lst Z Artdatabas</t>
-        </is>
-      </c>
+          <t>Jesper Wadstein, Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130930217</v>
+        <v>776085</v>
       </c>
       <c r="B8" t="n">
-        <v>79501</v>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6459</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällbergets NObrant, V om Hällsjön, V om Offerdals kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448392</v>
+        <v>448307</v>
       </c>
       <c r="R8" t="n">
-        <v>7037298</v>
+        <v>7037223</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1511,12 +1439,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2002-06-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2002-06-24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1525,44 +1453,43 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>granskog, på bark av levande rönn i 120 årig granskog,</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
+          <t>Rönn</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>malin almquist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Fabian Pettersson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130930226</v>
+        <v>776086</v>
       </c>
       <c r="B9" t="n">
-        <v>91830</v>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,33 +1497,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällbergets NObrant, V om Hällsjön, V om Offerdals kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>448362</v>
+        <v>448225</v>
       </c>
       <c r="R9" t="n">
-        <v>7037345</v>
+        <v>7037295</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1620,12 +1552,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2002-06-24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2002-06-24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1637,67 +1569,62 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>granskog, på bark av levande sälg i 120 årig granskog,</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
+          <t>Salix</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr"/>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>malin almquist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Fabian Pettersson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130930221</v>
+        <v>130930219</v>
       </c>
       <c r="B10" t="n">
-        <v>79716</v>
+        <v>92632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1797</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1707,10 +1634,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>448331</v>
+        <v>448355</v>
       </c>
       <c r="R10" t="n">
-        <v>7037320</v>
+        <v>7037273</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1789,10 +1716,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130930232</v>
+        <v>131523050</v>
       </c>
       <c r="B11" t="n">
-        <v>83223</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1800,34 +1727,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällberget Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>448438</v>
+        <v>448361</v>
       </c>
       <c r="R11" t="n">
-        <v>7037522</v>
+        <v>7037504</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1854,12 +1784,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1868,6 +1798,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1894,22 +1825,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Fabian Pettersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130930225</v>
+        <v>1923046</v>
       </c>
       <c r="B12" t="n">
-        <v>79716</v>
+        <v>75428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,37 +1848,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1797</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällbergets NObrant, V om Hällsjön, V om Offerdals kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>448356</v>
+        <v>448225</v>
       </c>
       <c r="R12" t="n">
-        <v>7037357</v>
+        <v>7037295</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1971,12 +1903,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2002-06-24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2002-06-24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1988,45 +1920,40 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>granskog, på bark av levande gran i 120 årig granskog,</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr"/>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>malin almquist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Fabian Pettersson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>130930227</v>
       </c>
       <c r="B13" t="n">
-        <v>83225</v>
+        <v>83307</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2140,32 +2067,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130930219</v>
+        <v>130930231</v>
       </c>
       <c r="B14" t="n">
-        <v>92532</v>
+        <v>83307</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2175,10 +2102,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448355</v>
+        <v>448412</v>
       </c>
       <c r="R14" t="n">
-        <v>7037273</v>
+        <v>7037419</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2257,10 +2184,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130930230</v>
+        <v>1963114</v>
       </c>
       <c r="B15" t="n">
-        <v>78257</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2268,37 +2195,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällbergets NObrant, V om Hällsjön, V om Offerdals kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>448404</v>
+        <v>448307</v>
       </c>
       <c r="R15" t="n">
-        <v>7037411</v>
+        <v>7037223</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2322,12 +2250,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2002-06-24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2002-06-24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2339,45 +2267,40 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>granskog, på bark av levande rönn i 120 årig granskog,</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
+          <t>Rönn</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr"/>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>malin almquist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Fabian Pettersson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130930220</v>
+        <v>1963115</v>
       </c>
       <c r="B16" t="n">
-        <v>79716</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2385,37 +2308,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1797</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hällberget, Jmt</t>
+          <t>Hällbergets NObrant, V om Hällsjön, V om Offerdals kyrka, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>448353</v>
+        <v>448225</v>
       </c>
       <c r="R16" t="n">
-        <v>7037267</v>
+        <v>7037295</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2439,12 +2363,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2002-06-24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2002-06-24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2456,45 +2380,40 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>granskog, på bark av levande sälg i 120 årig granskog,</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
+          <t>Salix</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr"/>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>malin almquist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Fabian Pettersson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>130930216</v>
       </c>
       <c r="B17" t="n">
-        <v>80350</v>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2607,45 +2526,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130930218</v>
+        <v>130930217</v>
       </c>
       <c r="B18" t="n">
-        <v>79716</v>
+        <v>79583</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1797</v>
+        <v>6459</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>448364</v>
+        <v>448392</v>
       </c>
       <c r="R18" t="n">
-        <v>7037293</v>
+        <v>7037298</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2686,27 +2608,23 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2724,32 +2642,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130930223</v>
+        <v>130930222</v>
       </c>
       <c r="B19" t="n">
-        <v>79716</v>
+        <v>83305</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1797</v>
+        <v>6486</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2759,10 +2677,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>448337</v>
+        <v>448330</v>
       </c>
       <c r="R19" t="n">
-        <v>7037328</v>
+        <v>7037323</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2841,32 +2759,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130930231</v>
+        <v>130930228</v>
       </c>
       <c r="B20" t="n">
-        <v>83225</v>
+        <v>83305</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6486</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2876,10 +2794,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448412</v>
+        <v>448370</v>
       </c>
       <c r="R20" t="n">
-        <v>7037419</v>
+        <v>7037362</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2958,10 +2876,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130930222</v>
+        <v>130930232</v>
       </c>
       <c r="B21" t="n">
-        <v>83223</v>
+        <v>83305</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2993,10 +2911,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448330</v>
+        <v>448438</v>
       </c>
       <c r="R21" t="n">
-        <v>7037323</v>
+        <v>7037522</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3075,45 +2993,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130930228</v>
+        <v>130864151</v>
       </c>
       <c r="B22" t="n">
-        <v>83223</v>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6486</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hällberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>448370</v>
+        <v>448506</v>
       </c>
       <c r="R22" t="n">
-        <v>7037362</v>
+        <v>7037495</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3148,6 +3074,11 @@
           <t>2026-01-24</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Födosöksspår efter hästmyror</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3156,26 +3087,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3192,10 +3103,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131064798</v>
+        <v>131064796</v>
       </c>
       <c r="B23" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3221,16 +3132,24 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lars-Olssved, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>448209</v>
+        <v>448214</v>
       </c>
       <c r="R23" t="n">
-        <v>7037284</v>
+        <v>7037299</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3267,14 +3186,14 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Troligt gammalt bohål ca 2,3m upp i granhögstubbe</t>
         </is>
       </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG23" t="b">
         <v>0</v>
@@ -3297,7 +3216,7 @@
         <v>131064797</v>
       </c>
       <c r="B24" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3396,10 +3315,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131064804</v>
+        <v>131064798</v>
       </c>
       <c r="B25" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3431,10 +3350,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>448308</v>
+        <v>448209</v>
       </c>
       <c r="R25" t="n">
-        <v>7037158</v>
+        <v>7037284</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3501,7 +3420,7 @@
         <v>131064799</v>
       </c>
       <c r="B26" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3600,10 +3519,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131064796</v>
+        <v>131064800</v>
       </c>
       <c r="B27" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3629,24 +3548,16 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lars-Olssved, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>448214</v>
+        <v>448227</v>
       </c>
       <c r="R27" t="n">
-        <v>7037299</v>
+        <v>7037255</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3683,14 +3594,14 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Troligt gammalt bohål ca 2,3m upp i granhögstubbe</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="b">
         <v>0</v>
@@ -3710,10 +3621,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131064802</v>
+        <v>131064801</v>
       </c>
       <c r="B28" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3745,7 +3656,7 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>448230</v>
+        <v>448214</v>
       </c>
       <c r="R28" t="n">
         <v>7037239</v>
@@ -3785,7 +3696,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3812,10 +3723,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131064800</v>
+        <v>131064802</v>
       </c>
       <c r="B29" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3847,10 +3758,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>448227</v>
+        <v>448230</v>
       </c>
       <c r="R29" t="n">
-        <v>7037255</v>
+        <v>7037239</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3887,7 +3798,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3911,6 +3822,327 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131064803</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lars-Olssved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>448227</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7037232</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131064804</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lars-Olssved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>448308</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7037158</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>130930230</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78339</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hällberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>448404</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7037411</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein, Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63441-2025 artfynd.xlsx
+++ b/artfynd/A 63441-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/441052</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130930218</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1019,6 +1034,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130930220</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130930221</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1253,6 +1278,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130930223</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1366,6 +1396,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/776085</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1479,6 +1514,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/776086</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1596,6 +1636,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130930219</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1709,6 +1754,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1923046</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1822,6 +1872,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1963114</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1933,6 +1988,11 @@
       <c r="AY12" t="inlineStr">
         <is>
           <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1963115</t>
         </is>
       </c>
     </row>
@@ -2051,6 +2111,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130930216</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2167,6 +2232,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130930217</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2284,6 +2354,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130930222</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2394,6 +2469,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064796</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2496,6 +2576,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064797</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2598,6 +2683,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064798</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2700,6 +2790,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064799</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2802,6 +2897,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064800</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2904,6 +3004,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064801</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3006,6 +3111,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064802</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3108,6 +3218,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064803</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3210,6 +3325,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131064804</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3327,6 +3447,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130930225</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3448,6 +3573,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131523050</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3565,6 +3695,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130930227</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3682,6 +3817,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130930231</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3799,6 +3939,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130930228</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3916,6 +4061,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130930232</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4026,6 +4176,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130864151</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4143,8 +4298,46 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130930230</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>